--- a/artfynd/A 19263-2025 artfynd.xlsx
+++ b/artfynd/A 19263-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,8 +774,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111363048</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 19263-2025 artfynd.xlsx
+++ b/artfynd/A 19263-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111363048</v>
+        <v>135581500</v>
       </c>
       <c r="B2" t="n">
-        <v>83307</v>
+        <v>80489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ödingen, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592710</v>
+        <v>592726</v>
       </c>
       <c r="R2" t="n">
-        <v>6985255</v>
+        <v>6985185</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,19 +762,136 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581500</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>111363048</v>
+      </c>
+      <c r="B3" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>592710</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6985255</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-08-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-08-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/111363048</t>
         </is>
@@ -783,6 +900,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19263-2025 artfynd.xlsx
+++ b/artfynd/A 19263-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135581500</v>
       </c>
       <c r="B2" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19263-2025 artfynd.xlsx
+++ b/artfynd/A 19263-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135581500</v>
       </c>
       <c r="B2" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19263-2025 artfynd.xlsx
+++ b/artfynd/A 19263-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111363048</v>
+        <v>135581500</v>
       </c>
       <c r="B2" t="n">
-        <v>83307</v>
+        <v>80557</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ödingen, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592710</v>
+        <v>592726</v>
       </c>
       <c r="R2" t="n">
-        <v>6985255</v>
+        <v>6985185</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,19 +762,136 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581500</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>111363048</v>
+      </c>
+      <c r="B3" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>592710</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6985255</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-08-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-08-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/111363048</t>
         </is>
@@ -783,6 +900,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19263-2025 artfynd.xlsx
+++ b/artfynd/A 19263-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135581500</v>
       </c>
       <c r="B2" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19263-2025 artfynd.xlsx
+++ b/artfynd/A 19263-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135581500</v>
       </c>
       <c r="B2" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
